--- a/UZr/UMo-UZr_AIMD.xlsx
+++ b/UZr/UMo-UZr_AIMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/UZr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664D4A27-C78E-CC4C-9EB6-CB7E1641B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF26664C-D1C4-304C-B681-B4F410064F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="500" windowWidth="21820" windowHeight="15800" activeTab="1" xr2:uid="{73DE5FDA-00CA-FC43-83AF-91CA67D3B0B2}"/>
+    <workbookView xWindow="5060" yWindow="1960" windowWidth="21820" windowHeight="15800" activeTab="1" xr2:uid="{73DE5FDA-00CA-FC43-83AF-91CA67D3B0B2}"/>
   </bookViews>
   <sheets>
     <sheet name="UMo" sheetId="1" r:id="rId1"/>
@@ -10736,6 +10736,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10743,7 +10744,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19988,6 +19988,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19995,7 +19996,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
